--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\10-09-02 Finanz- &amp; Kontrollanwendungen\Benutzer\Berger\ASVNeufeld\2025_26\Planung 2025_26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E930D9-9AB8-467B-B79F-7DB2272CDECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDB3E47-96F0-4BE7-B1E0-406A869BD9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -277,8 +280,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="hh:mm;@"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="hh:mm;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -525,7 +528,7 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -549,7 +552,7 @@
     <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -785,20 +788,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -824,7 +827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -854,7 +857,7 @@
         <v>TADTEN</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>4</v>
       </c>
@@ -884,7 +887,7 @@
         <v>ILLMITZ</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>6</v>
       </c>
@@ -914,7 +917,7 @@
         <v>STEINBRUNN</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>8</v>
       </c>
@@ -944,7 +947,7 @@
         <v>HORNSTEIN</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>10</v>
       </c>
@@ -974,7 +977,7 @@
         <v>PAMA</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>13</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>KITTSEE</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>2</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>TADTEN</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>ILLMITZ</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>STEINBRUNN</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -1124,7 +1127,7 @@
         <v>HORNSTEIN</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>PAMA</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>KITTSEE</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
         <v>15</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>SPG SVO-EDELSERPENTIN</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
         <v>17</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>SPG DER CLUB/KIRCHSCHLAG</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
         <v>19</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>SV LEITHAPRODERSDORF</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
         <v>21</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>SV BB1 WOLFAU</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
         <v>23</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>ST. GEORGEN/EISENSTADT</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>25</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>SC/ESV PARNDORF 1919</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>26</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>FC GROßHÖFLEIN</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>28</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>SPG ROSALIA/MARZ</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>32</v>
       </c>
@@ -1454,7 +1457,7 @@
         <v>SC NEUSIEDL AM SEE 1919</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24">
         <v>34</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>SV WULKAPRODERSDORF</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="24">
         <v>37</v>
       </c>
@@ -1515,7 +1518,7 @@
       </c>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="24">
         <v>40</v>
       </c>
@@ -1546,7 +1549,7 @@
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="24">
         <v>41</v>
       </c>
@@ -1577,7 +1580,7 @@
       </c>
       <c r="J26" s="23"/>
     </row>
-    <row r="27" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>44</v>
       </c>
@@ -1607,7 +1610,7 @@
         <v>SC KITTSEE</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>47</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>SPG BREITENBRUNN/PURBACH/WINDEN</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>51</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>SC EISENSTADT/RUST</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>53</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>SPG LEITHA/STOTZING</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="25">
         <v>55</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>SPG WAHA ST. MARGARETHEN</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="25">
         <v>57</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>STOTZING</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
         <v>59</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>STEINBRUNN</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="25">
         <v>61</v>
       </c>
@@ -1817,7 +1820,7 @@
         <v>SPG KLIMPUH</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
         <v>64</v>
       </c>
@@ -1846,7 +1849,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="31">
         <v>69</v>
       </c>
@@ -1875,7 +1878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>74</v>
       </c>
@@ -1904,7 +1907,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>79</v>
       </c>
@@ -1934,7 +1937,7 @@
         <v>TECO 7 CAMP</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>80</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>TECO 7 CAMP</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>81</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>TECO 7 CAMP</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>82</v>
       </c>
@@ -2024,7 +2027,7 @@
         <v>GGG - QUALIFIKATION</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>83</v>
       </c>
@@ -2073,15 +2076,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6365EA26-3DBC-4E60-A609-E8FEDD19B7F6}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.28515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="46"/>
-    <col min="3" max="4" width="11.42578125" style="36"/>
-    <col min="5" max="6" width="11.42578125" style="49"/>
+    <col min="1" max="1" width="50.33203125" style="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="46"/>
+    <col min="3" max="4" width="11.44140625" style="36"/>
+    <col min="5" max="6" width="11.44140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>46</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I2</f>
         <v>ASV NEUFELD -TADTEN</v>
@@ -2111,12 +2114,11 @@
         <v>46102</v>
       </c>
       <c r="C2" s="36">
-        <f>'Nach Mannschaften sortiert'!E2</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D2" s="36">
         <f>C2+"1:45"</f>
-        <v>0.73958333333333326</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E2" s="49" t="str">
         <f>'Nach Mannschaften sortiert'!F2</f>
@@ -2127,7 +2129,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I3</f>
         <v>ASV NEUFELD -ILLMITZ</v>
@@ -2153,7 +2155,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I4</f>
         <v>ASV NEUFELD -STEINBRUNN</v>
@@ -2179,7 +2181,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I5</f>
         <v>ASV NEUFELD -HORNSTEIN</v>
@@ -2205,7 +2207,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I6</f>
         <v>ASV NEUFELD -PAMA</v>
@@ -2231,7 +2233,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I7</f>
         <v>ASV NEUFELD -KITTSEE</v>
@@ -2257,7 +2259,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I8</f>
         <v>ASV NEUFELD -TADTEN</v>
@@ -2283,7 +2285,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I9</f>
         <v>ASV NEUFELD -ILLMITZ</v>
@@ -2309,7 +2311,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I10</f>
         <v>ASV NEUFELD -STEINBRUNN</v>
@@ -2335,7 +2337,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I11</f>
         <v>ASV NEUFELD -HORNSTEIN</v>
@@ -2361,7 +2363,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I12</f>
         <v>ASV NEUFELD -PAMA</v>
@@ -2387,7 +2389,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I13</f>
         <v>ASV NEUFELD -KITTSEE</v>
@@ -2413,7 +2415,7 @@
         <v>RESERVE</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I15</f>
         <v>ASV NEUFELD -SPG DER CLUB/KIRCHSCHLAG</v>
@@ -2439,7 +2441,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I18</f>
         <v>ASV NEUFELD -ST. GEORGEN/EISENSTADT</v>
@@ -2465,7 +2467,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I19</f>
         <v>ASV NEUFELD -SC/ESV PARNDORF 1919</v>
@@ -2491,7 +2493,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I21</f>
         <v>ASV NEUFELD -SPG ROSALIA/MARZ</v>
@@ -2517,7 +2519,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I23</f>
         <v>ASV NEUFELD -SV WULKAPRODERSDORF</v>
@@ -2543,7 +2545,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I24</f>
         <v>ASV NEUFELD -SPG LEITHA/STOTZING</v>
@@ -2569,7 +2571,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I25</f>
         <v>ASV NEUFELD -SK PAMA</v>
@@ -2595,7 +2597,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I26</f>
         <v>ASV NEUFELD -SC KITTSEE</v>
@@ -2621,7 +2623,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I27</f>
         <v>ASV NEUFELD -SC KITTSEE</v>
@@ -2647,7 +2649,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I28</f>
         <v>ASV NEUFELD -SPG BREITENBRUNN/PURBACH/WINDEN</v>
@@ -2673,7 +2675,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I29</f>
         <v>ASV NEUFELD -SC EISENSTADT/RUST</v>
@@ -2699,7 +2701,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I30</f>
         <v>ASV NEUFELD -SPG LEITHA/STOTZING</v>
@@ -2725,7 +2727,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I31</f>
         <v>ASV NEUFELD -SPG WAHA ST. MARGARETHEN</v>
@@ -2751,7 +2753,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I32</f>
         <v>ASV NEUFELD -STOTZING</v>
@@ -2777,7 +2779,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I33</f>
         <v>ASV NEUFELD -STEINBRUNN</v>
@@ -2803,7 +2805,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I34</f>
         <v>ASV NEUFELD -SPG KLIMPUH</v>
@@ -2829,7 +2831,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I35</f>
         <v>ASV NEUFELD -VIELE</v>
@@ -2854,7 +2856,7 @@
         <v>U9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I36</f>
         <v>ASV NEUFELD -VIELE</v>
@@ -2879,7 +2881,7 @@
         <v>U8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I37</f>
         <v>ASV NEUFELD -VIELE</v>
@@ -2904,7 +2906,7 @@
         <v>U7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I38</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
@@ -2929,7 +2931,7 @@
         <v>Nachwuchscamp</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I39</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
@@ -2954,7 +2956,7 @@
         <v>Nachwuchscamp</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I40</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
@@ -2979,7 +2981,7 @@
         <v>Nachwuchscamp</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I41</f>
         <v>ASV NEUFELD -GGG - QUALIFIKATION</v>
@@ -3004,7 +3006,7 @@
         <v>U9-Turnier</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="49" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I42</f>
         <v>ASV NEUFELD -9. GGG</v>
@@ -3038,109 +3040,109 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7379293C-A1E0-4DC6-BEBB-D0F5058BC12D}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDB3E47-96F0-4BE7-B1E0-406A869BD9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E4BA1-74F1-4193-8E4E-EF8D32998794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2114,11 +2114,11 @@
         <v>46102</v>
       </c>
       <c r="C2" s="36">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="36">
         <f>C2+"1:45"</f>
-        <v>0.69791666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E2" s="49" t="str">
         <f>'Nach Mannschaften sortiert'!F2</f>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E4BA1-74F1-4193-8E4E-EF8D32998794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C41007-BA5F-4E0B-8383-2598262C0A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,9 +205,6 @@
     <t>RESERVE</t>
   </si>
   <si>
-    <t>VIELE</t>
-  </si>
-  <si>
     <t>Nachwuchscamp</t>
   </si>
   <si>
@@ -272,6 +269,9 @@
   </si>
   <si>
     <t>df = pd.read_excel("Terminefussball_2026_Frühjahr_TestICS.xlsx", sheet_name="ICS")</t>
+  </si>
+  <si>
+    <t>verschiedene Gegner</t>
   </si>
 </sst>
 </file>
@@ -385,7 +385,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -421,11 +421,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,6 +567,10 @@
     <xf numFmtId="20" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1845,8 +1860,8 @@
       <c r="H35" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I35" t="s">
-        <v>55</v>
+      <c r="I35" s="51" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1874,8 +1889,8 @@
       <c r="H36" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="I36" t="s">
-        <v>55</v>
+      <c r="I36" s="51" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1903,8 +1918,8 @@
       <c r="H37" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="I37" t="s">
-        <v>55</v>
+      <c r="I37" s="51" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1915,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="44">
         <v>46111</v>
@@ -1945,7 +1960,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" s="44">
         <v>46112</v>
@@ -1975,7 +1990,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="44">
         <v>46113</v>
@@ -2005,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="45">
         <v>46186</v>
@@ -2035,7 +2050,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="45">
         <v>46256</v>
@@ -2078,14 +2093,14 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.33203125" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.33203125" style="50" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.44140625" style="46"/>
     <col min="3" max="4" width="11.44140625" style="36"/>
     <col min="5" max="6" width="11.44140625" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="46" t="s">
@@ -2105,9 +2120,9 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I2</f>
-        <v>ASV NEUFELD -TADTEN</v>
+      <c r="A2" s="50" t="str">
+        <f>F2 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I2</f>
+        <v>KM ASV -TADTEN</v>
       </c>
       <c r="B2" s="46">
         <f>'Nach Mannschaften sortiert'!D2</f>
@@ -2130,9 +2145,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I3</f>
-        <v>ASV NEUFELD -ILLMITZ</v>
+      <c r="A3" s="50" t="str">
+        <f>F3 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I3</f>
+        <v>KM ASV -ILLMITZ</v>
       </c>
       <c r="B3" s="46">
         <f>'Nach Mannschaften sortiert'!D3</f>
@@ -2156,9 +2171,9 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I4</f>
-        <v>ASV NEUFELD -STEINBRUNN</v>
+      <c r="A4" s="50" t="str">
+        <f>F4 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I4</f>
+        <v>KM ASV -STEINBRUNN</v>
       </c>
       <c r="B4" s="46">
         <f>'Nach Mannschaften sortiert'!D4</f>
@@ -2182,9 +2197,9 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I5</f>
-        <v>ASV NEUFELD -HORNSTEIN</v>
+      <c r="A5" s="50" t="str">
+        <f>F5 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I5</f>
+        <v>KM ASV -HORNSTEIN</v>
       </c>
       <c r="B5" s="46">
         <f>'Nach Mannschaften sortiert'!D5</f>
@@ -2208,9 +2223,9 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I6</f>
-        <v>ASV NEUFELD -PAMA</v>
+      <c r="A6" s="50" t="str">
+        <f>F6 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I6</f>
+        <v>KM ASV -PAMA</v>
       </c>
       <c r="B6" s="46">
         <f>'Nach Mannschaften sortiert'!D6</f>
@@ -2234,9 +2249,9 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I7</f>
-        <v>ASV NEUFELD -KITTSEE</v>
+      <c r="A7" s="50" t="str">
+        <f>F7 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I7</f>
+        <v>KM ASV -KITTSEE</v>
       </c>
       <c r="B7" s="46">
         <f>'Nach Mannschaften sortiert'!D7</f>
@@ -2260,9 +2275,9 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I8</f>
-        <v>ASV NEUFELD -TADTEN</v>
+      <c r="A8" s="50" t="str">
+        <f>F8 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I8</f>
+        <v>RESERVE ASV -TADTEN</v>
       </c>
       <c r="B8" s="46">
         <f>'Nach Mannschaften sortiert'!D8</f>
@@ -2286,9 +2301,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I9</f>
-        <v>ASV NEUFELD -ILLMITZ</v>
+      <c r="A9" s="50" t="str">
+        <f>F9 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I9</f>
+        <v>RESERVE ASV -ILLMITZ</v>
       </c>
       <c r="B9" s="46">
         <f>'Nach Mannschaften sortiert'!D9</f>
@@ -2312,9 +2327,9 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I10</f>
-        <v>ASV NEUFELD -STEINBRUNN</v>
+      <c r="A10" s="50" t="str">
+        <f>F10 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I10</f>
+        <v>RESERVE ASV -STEINBRUNN</v>
       </c>
       <c r="B10" s="46">
         <f>'Nach Mannschaften sortiert'!D10</f>
@@ -2338,9 +2353,9 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I11</f>
-        <v>ASV NEUFELD -HORNSTEIN</v>
+      <c r="A11" s="50" t="str">
+        <f>F11 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I11</f>
+        <v>RESERVE ASV -HORNSTEIN</v>
       </c>
       <c r="B11" s="46">
         <f>'Nach Mannschaften sortiert'!D11</f>
@@ -2364,9 +2379,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I12</f>
-        <v>ASV NEUFELD -PAMA</v>
+      <c r="A12" s="50" t="str">
+        <f>F12 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I12</f>
+        <v>RESERVE ASV -PAMA</v>
       </c>
       <c r="B12" s="46">
         <f>'Nach Mannschaften sortiert'!D12</f>
@@ -2390,9 +2405,9 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I13</f>
-        <v>ASV NEUFELD -KITTSEE</v>
+      <c r="A13" s="50" t="str">
+        <f>F13 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I13</f>
+        <v>RESERVE ASV -KITTSEE</v>
       </c>
       <c r="B13" s="46">
         <f>'Nach Mannschaften sortiert'!D13</f>
@@ -2416,9 +2431,9 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I15</f>
-        <v>ASV NEUFELD -SPG DER CLUB/KIRCHSCHLAG</v>
+      <c r="A14" s="50" t="str">
+        <f>F14 &amp;  " ASV -" &amp; 'Nach Mannschaften sortiert'!I15</f>
+        <v>U16 ASV -SPG DER CLUB/KIRCHSCHLAG</v>
       </c>
       <c r="B14" s="46">
         <f>'Nach Mannschaften sortiert'!D15</f>
@@ -2442,9 +2457,9 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I18</f>
-        <v>ASV NEUFELD -ST. GEORGEN/EISENSTADT</v>
+      <c r="A15" s="50" t="str">
+        <f>F15 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I18</f>
+        <v>U16 ASV -ST. GEORGEN/EISENSTADT</v>
       </c>
       <c r="B15" s="46">
         <f>'Nach Mannschaften sortiert'!D18</f>
@@ -2468,9 +2483,9 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I19</f>
-        <v>ASV NEUFELD -SC/ESV PARNDORF 1919</v>
+      <c r="A16" s="50" t="str">
+        <f>F16 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I19</f>
+        <v>U15 ASV -SC/ESV PARNDORF 1919</v>
       </c>
       <c r="B16" s="46">
         <f>'Nach Mannschaften sortiert'!D19</f>
@@ -2494,9 +2509,9 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I21</f>
-        <v>ASV NEUFELD -SPG ROSALIA/MARZ</v>
+      <c r="A17" s="50" t="str">
+        <f>F17 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I21</f>
+        <v>U15 ASV -SPG ROSALIA/MARZ</v>
       </c>
       <c r="B17" s="46">
         <f>'Nach Mannschaften sortiert'!D21</f>
@@ -2520,9 +2535,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I23</f>
-        <v>ASV NEUFELD -SV WULKAPRODERSDORF</v>
+      <c r="A18" s="50" t="str">
+        <f>F18 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I23</f>
+        <v>U14 ASV -SV WULKAPRODERSDORF</v>
       </c>
       <c r="B18" s="46">
         <f>'Nach Mannschaften sortiert'!D23</f>
@@ -2546,9 +2561,9 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I24</f>
-        <v>ASV NEUFELD -SPG LEITHA/STOTZING</v>
+      <c r="A19" s="50" t="str">
+        <f>F19 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I24</f>
+        <v>U14 ASV -SPG LEITHA/STOTZING</v>
       </c>
       <c r="B19" s="46">
         <f>'Nach Mannschaften sortiert'!D24</f>
@@ -2572,9 +2587,9 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I25</f>
-        <v>ASV NEUFELD -SK PAMA</v>
+      <c r="A20" s="50" t="str">
+        <f>F20 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I25</f>
+        <v>U14 ASV -SK PAMA</v>
       </c>
       <c r="B20" s="46">
         <f>'Nach Mannschaften sortiert'!D25</f>
@@ -2598,9 +2613,9 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I26</f>
-        <v>ASV NEUFELD -SC KITTSEE</v>
+      <c r="A21" s="50" t="str">
+        <f>F21 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I26</f>
+        <v>U14 ASV -SC KITTSEE</v>
       </c>
       <c r="B21" s="46">
         <f>'Nach Mannschaften sortiert'!D26</f>
@@ -2624,9 +2639,9 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I27</f>
-        <v>ASV NEUFELD -SC KITTSEE</v>
+      <c r="A22" s="50" t="str">
+        <f>F22 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I27</f>
+        <v>U13 ASV -SC KITTSEE</v>
       </c>
       <c r="B22" s="46">
         <f>'Nach Mannschaften sortiert'!D27</f>
@@ -2650,9 +2665,9 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I28</f>
-        <v>ASV NEUFELD -SPG BREITENBRUNN/PURBACH/WINDEN</v>
+      <c r="A23" s="50" t="str">
+        <f>F23 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I28</f>
+        <v>U13 ASV -SPG BREITENBRUNN/PURBACH/WINDEN</v>
       </c>
       <c r="B23" s="46">
         <f>'Nach Mannschaften sortiert'!D28</f>
@@ -2676,9 +2691,9 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I29</f>
-        <v>ASV NEUFELD -SC EISENSTADT/RUST</v>
+      <c r="A24" s="50" t="str">
+        <f>F24 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I29</f>
+        <v>U13 ASV -SC EISENSTADT/RUST</v>
       </c>
       <c r="B24" s="46">
         <f>'Nach Mannschaften sortiert'!D29</f>
@@ -2702,9 +2717,9 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I30</f>
-        <v>ASV NEUFELD -SPG LEITHA/STOTZING</v>
+      <c r="A25" s="50" t="str">
+        <f>F25 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I30</f>
+        <v>U13 ASV -SPG LEITHA/STOTZING</v>
       </c>
       <c r="B25" s="46">
         <f>'Nach Mannschaften sortiert'!D30</f>
@@ -2728,9 +2743,9 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I31</f>
-        <v>ASV NEUFELD -SPG WAHA ST. MARGARETHEN</v>
+      <c r="A26" s="50" t="str">
+        <f>F26 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I31</f>
+        <v>U11 ASV -SPG WAHA ST. MARGARETHEN</v>
       </c>
       <c r="B26" s="46">
         <f>'Nach Mannschaften sortiert'!D31</f>
@@ -2754,9 +2769,9 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I32</f>
-        <v>ASV NEUFELD -STOTZING</v>
+      <c r="A27" s="50" t="str">
+        <f>F27 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I32</f>
+        <v>U11 ASV -STOTZING</v>
       </c>
       <c r="B27" s="46">
         <f>'Nach Mannschaften sortiert'!D32</f>
@@ -2780,9 +2795,9 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I33</f>
-        <v>ASV NEUFELD -STEINBRUNN</v>
+      <c r="A28" s="50" t="str">
+        <f>F28 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I33</f>
+        <v>U11 ASV -STEINBRUNN</v>
       </c>
       <c r="B28" s="46">
         <f>'Nach Mannschaften sortiert'!D33</f>
@@ -2806,9 +2821,9 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I34</f>
-        <v>ASV NEUFELD -SPG KLIMPUH</v>
+      <c r="A29" s="50" t="str">
+        <f>F29 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I34</f>
+        <v>U11 ASV -SPG KLIMPUH</v>
       </c>
       <c r="B29" s="46">
         <f>'Nach Mannschaften sortiert'!D34</f>
@@ -2832,9 +2847,9 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I35</f>
-        <v>ASV NEUFELD -VIELE</v>
+      <c r="A30" s="50" t="str">
+        <f>F30 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I35</f>
+        <v>U9 ASV -verschiedene Gegner</v>
       </c>
       <c r="B30" s="46">
         <f>'Nach Mannschaften sortiert'!D35</f>
@@ -2857,9 +2872,9 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I36</f>
-        <v>ASV NEUFELD -VIELE</v>
+      <c r="A31" s="50" t="str">
+        <f>F31 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I36</f>
+        <v>U8 ASV -verschiedene Gegner</v>
       </c>
       <c r="B31" s="46">
         <f>'Nach Mannschaften sortiert'!D36</f>
@@ -2882,9 +2897,9 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49" t="str">
-        <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I37</f>
-        <v>ASV NEUFELD -VIELE</v>
+      <c r="A32" s="50" t="str">
+        <f>F32 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I37</f>
+        <v>U7 ASV -verschiedene Gegner</v>
       </c>
       <c r="B32" s="46">
         <f>'Nach Mannschaften sortiert'!D37</f>
@@ -2907,7 +2922,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="49" t="str">
+      <c r="A33" s="50" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I38</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
       </c>
@@ -2932,7 +2947,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="str">
+      <c r="A34" s="50" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I39</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
       </c>
@@ -2957,7 +2972,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49" t="str">
+      <c r="A35" s="50" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I40</f>
         <v>ASV NEUFELD -TECO 7 CAMP</v>
       </c>
@@ -2982,7 +2997,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="49" t="str">
+      <c r="A36" s="50" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I41</f>
         <v>ASV NEUFELD -GGG - QUALIFIKATION</v>
       </c>
@@ -3007,7 +3022,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="49" t="str">
+      <c r="A37" s="50" t="str">
         <f>"ASV NEUFELD -" &amp; 'Nach Mannschaften sortiert'!I42</f>
         <v>ASV NEUFELD -9. GGG</v>
       </c>
@@ -3044,107 +3059,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C41007-BA5F-4E0B-8383-2598262C0A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F0EB69-B0CF-4202-9BAD-0ECB37E1CBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2536,8 +2536,8 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="str">
-        <f>F18 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I23</f>
-        <v>U14 ASV -SV WULKAPRODERSDORF</v>
+        <f>"AGESAGT!!!!"&amp;F18 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I23</f>
+        <v>AGESAGT!!!!U14 ASV -SV WULKAPRODERSDORF</v>
       </c>
       <c r="B18" s="46">
         <f>'Nach Mannschaften sortiert'!D23</f>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F0EB69-B0CF-4202-9BAD-0ECB37E1CBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B22FFF8-EF41-4141-834A-D184E7276AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2666,8 +2666,8 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="str">
-        <f>F23 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I28</f>
-        <v>U13 ASV -SPG BREITENBRUNN/PURBACH/WINDEN</v>
+        <f>"AGESAGT!!!!"&amp;F23 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I28</f>
+        <v>AGESAGT!!!!U13 ASV -SPG BREITENBRUNN/PURBACH/WINDEN</v>
       </c>
       <c r="B23" s="46">
         <f>'Nach Mannschaften sortiert'!D28</f>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B22FFF8-EF41-4141-834A-D184E7276AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1136F38E-B070-4012-BF83-41048D1D6F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Heimspiele_ASVNEUFELD_ICS.xlsx
+++ b/Heimspiele_ASVNEUFELD_ICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1136F38E-B070-4012-BF83-41048D1D6F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1B87DF-A065-48CA-AF8D-787BD1ACAD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2640,8 +2640,8 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="50" t="str">
-        <f>F22 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I27</f>
-        <v>U13 ASV -SC KITTSEE</v>
+        <f>"AGESAGT!!!!"&amp;F22 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I27</f>
+        <v>AGESAGT!!!!U13 ASV -SC KITTSEE</v>
       </c>
       <c r="B22" s="46">
         <f>'Nach Mannschaften sortiert'!D27</f>
@@ -2666,8 +2666,8 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="str">
-        <f>"AGESAGT!!!!"&amp;F23 &amp; " ASV -" &amp; 'Nach Mannschaften sortiert'!I28</f>
-        <v>AGESAGT!!!!U13 ASV -SPG BREITENBRUNN/PURBACH/WINDEN</v>
+        <f>F23&amp;" ASV -"&amp;'Nach Mannschaften sortiert'!I28</f>
+        <v>U13 ASV -SPG BREITENBRUNN/PURBACH/WINDEN</v>
       </c>
       <c r="B23" s="46">
         <f>'Nach Mannschaften sortiert'!D28</f>
